--- a/artfynd/A 71055-2021 artfynd.xlsx
+++ b/artfynd/A 71055-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 71055-2021 artfynd.xlsx
+++ b/artfynd/A 71055-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,19 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113963390</v>
+        <v>105479325</v>
       </c>
       <c r="B2" t="n">
-        <v>101952</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>103403</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -715,14 +710,14 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Blentarp, Sk</t>
+          <t>Skåne, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>411302</v>
+        <v>411300</v>
       </c>
       <c r="R2" t="n">
-        <v>6161065</v>
+        <v>6161074</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -747,26 +742,21 @@
           <t>Blentarp</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>3cd73322-b24e-4837-a5e6-9678038dfb48</t>
-        </is>
-      </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-06-07</t>
+          <t>2011-04-04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-06-07</t>
+          <t>2011-04-04</t>
         </is>
       </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="b">
         <v>0</v>
@@ -783,6 +773,116 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr">
+        <is>
+          <t>Skyddsvärda träd</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>113963390</v>
+      </c>
+      <c r="B3" t="n">
+        <v>103403</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>223246</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Blentarp, Sk</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>411302</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6161065</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Sjöbo</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Blentarp</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>3cd73322-b24e-4837-a5e6-9678038dfb48</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2023-06-07</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2023-06-07</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Torbjörn Blixt</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Via Torbjörn Blixt</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
         <is>
           <t>Skyddsvärda träd</t>
         </is>
